--- a/confidential/expnstrck.xlsx
+++ b/confidential/expnstrck.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chakitan.vyas\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDC8FB3-40C8-4867-9D5A-287441B157D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED966B56-642A-4FD9-AA79-53841A77EFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="350" windowWidth="19420" windowHeight="10560" xr2:uid="{964BC787-0575-427E-8B64-7602985136CD}"/>
+    <workbookView xWindow="-110" yWindow="350" windowWidth="19420" windowHeight="10560" activeTab="3" xr2:uid="{964BC787-0575-427E-8B64-7602985136CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Track Expense" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
-    <sheet name="mama" sheetId="4" r:id="rId3"/>
-    <sheet name="Cutoff" sheetId="5" r:id="rId4"/>
+    <sheet name="Maa" sheetId="4" r:id="rId2"/>
+    <sheet name="Cutoff" sheetId="5" r:id="rId3"/>
+    <sheet name="Misc" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">mama!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Maa!$A$6:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Track Expense'!$A$1:$K$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,30 +40,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="371">
   <si>
     <t>Home</t>
   </si>
@@ -164,21 +142,9 @@
     <t>Diversify Portfolio</t>
   </si>
   <si>
-    <t>12K Redeemed from MF-</t>
-  </si>
-  <si>
-    <t>For Diversifying Portfolio</t>
-  </si>
-  <si>
-    <t>5K - Debt MF || 5K - International MF</t>
-  </si>
-  <si>
     <t>Equity</t>
   </si>
   <si>
-    <t>Gold</t>
-  </si>
-  <si>
     <t>Debt</t>
   </si>
   <si>
@@ -188,9 +154,6 @@
     <t>STOCK</t>
   </si>
   <si>
-    <t>AUGMONT</t>
-  </si>
-  <si>
     <t>Date\Bank</t>
   </si>
   <si>
@@ -260,9 +223,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>NOT DONE</t>
-  </si>
-  <si>
     <t>DONE</t>
   </si>
   <si>
@@ -272,9 +232,6 @@
     <t>International</t>
   </si>
   <si>
-    <t>Silver</t>
-  </si>
-  <si>
     <t>7-Union Balanced Advantage Fund Direct Growth</t>
   </si>
   <si>
@@ -314,9 +271,6 @@
     <t>upstox</t>
   </si>
   <si>
-    <t>5th of Month[Start Jun'21]</t>
-  </si>
-  <si>
     <t>JAN</t>
   </si>
   <si>
@@ -410,9 +364,6 @@
     <t>JUN</t>
   </si>
   <si>
-    <t>Invested in Stock Instead</t>
-  </si>
-  <si>
     <t>Paytm</t>
   </si>
   <si>
@@ -443,51 +394,6 @@
     <t>Pune Trip FF</t>
   </si>
   <si>
-    <t>&amp;Flix</t>
-  </si>
-  <si>
-    <t>Sony Pix HD</t>
-  </si>
-  <si>
-    <t>Sony HD</t>
-  </si>
-  <si>
-    <t>Sony Max HD</t>
-  </si>
-  <si>
-    <t>UTV HD</t>
-  </si>
-  <si>
-    <t>Star Gold HD</t>
-  </si>
-  <si>
-    <t>&amp;TV HD</t>
-  </si>
-  <si>
-    <t>Zee Cinema HD</t>
-  </si>
-  <si>
-    <t>&amp;Pictures HD</t>
-  </si>
-  <si>
-    <t>Zee News</t>
-  </si>
-  <si>
-    <t>Aaj Tak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovery </t>
-  </si>
-  <si>
-    <t>Zee Talkies</t>
-  </si>
-  <si>
-    <t>Marathi News</t>
-  </si>
-  <si>
-    <t>Star Sports HD hindi</t>
-  </si>
-  <si>
     <t>GharKharch</t>
   </si>
   <si>
@@ -518,33 +424,6 @@
     <t>icici credit card az</t>
   </si>
   <si>
-    <t>Installment No</t>
-  </si>
-  <si>
-    <t>Principal</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>Balance Amount</t>
-  </si>
-  <si>
-    <t>One time processing Fee</t>
-  </si>
-  <si>
-    <t>GST on Interest</t>
-  </si>
-  <si>
-    <t>Actual EMI</t>
-  </si>
-  <si>
-    <t>Proposed EMI Amount</t>
-  </si>
-  <si>
-    <t>Cut 2000 from DBS - below is remaining amount</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -578,9 +457,6 @@
     <t>W/N</t>
   </si>
   <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
     <t>17th of Month [*TAX SAVING]</t>
   </si>
   <si>
@@ -602,18 +478,12 @@
     <t>[* TAX SAVING]</t>
   </si>
   <si>
-    <t>Cutoff through Month</t>
-  </si>
-  <si>
     <t>Invesment Performance</t>
   </si>
   <si>
     <t>Jindal</t>
   </si>
   <si>
-    <t>as of 30JUL'22</t>
-  </si>
-  <si>
     <t>x6</t>
   </si>
   <si>
@@ -701,15 +571,6 @@
     <t>x201</t>
   </si>
   <si>
-    <t>1: MBA</t>
-  </si>
-  <si>
-    <t>3: DEBT CLEARANCE : MATTRESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2: RAISE MONEY </t>
-  </si>
-  <si>
     <t>Side Hustle</t>
   </si>
   <si>
@@ -728,9 +589,6 @@
     <t>Keep but Switch to New</t>
   </si>
   <si>
-    <t>Long Keep</t>
-  </si>
-  <si>
     <t>Short Keep</t>
   </si>
   <si>
@@ -740,9 +598,6 @@
     <t xml:space="preserve">[^ 4months EMI for Magoosh - then back to ShortTerm/Savings-PNB] </t>
   </si>
   <si>
-    <t>[^ 6months only - then merge to Home/InCash-DBS]</t>
-  </si>
-  <si>
     <t>Savings %</t>
   </si>
   <si>
@@ -755,12 +610,6 @@
     <t>Parag Parikh[25th of Month][Start Aug'21][End Sep'22][% IMNVEST to CLEAR DEBT]</t>
   </si>
   <si>
-    <t>GROSS SALARY</t>
-  </si>
-  <si>
-    <t>Earnings</t>
-  </si>
-  <si>
     <t>Amount</t>
   </si>
   <si>
@@ -785,12 +634,6 @@
     <t>Internet A</t>
   </si>
   <si>
-    <t>DEDUCTIONS</t>
-  </si>
-  <si>
-    <t>Deductions</t>
-  </si>
-  <si>
     <t>PF</t>
   </si>
   <si>
@@ -800,9 +643,6 @@
     <t>TDS</t>
   </si>
   <si>
-    <t>IN-HAND</t>
-  </si>
-  <si>
     <t>Overall Tax Summary (Actual)</t>
   </si>
   <si>
@@ -1019,40 +859,301 @@
     <t>Variable P</t>
   </si>
   <si>
-    <t>Leaves</t>
-  </si>
-  <si>
-    <t>Variable Pay</t>
-  </si>
-  <si>
-    <t>In-hand salary</t>
-  </si>
-  <si>
-    <t>internation exposure - onsite oppo.</t>
-  </si>
-  <si>
-    <t>commute</t>
-  </si>
-  <si>
-    <t>EMI Amount</t>
-  </si>
-  <si>
-    <t>hours of work</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>9--6</t>
-  </si>
-  <si>
-    <t>22+8+15</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>designation - level</t>
+    <t>Tirupati Trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear in CC Bill NOV </t>
+  </si>
+  <si>
+    <t>For Furniture 7.5K total</t>
+  </si>
+  <si>
+    <t>for flat fittings</t>
+  </si>
+  <si>
+    <t>Return in DEC</t>
+  </si>
+  <si>
+    <t>Ghee 1950 total</t>
+  </si>
+  <si>
+    <t>Tirupati Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">take from Ruchi </t>
+  </si>
+  <si>
+    <t>Pune trip fastag</t>
+  </si>
+  <si>
+    <t>Hyd Trip fastag</t>
+  </si>
+  <si>
+    <t>Hyd Trip Petrol</t>
+  </si>
+  <si>
+    <t>Pune plumbing work</t>
+  </si>
+  <si>
+    <t>Clear in CC Bill FEB</t>
+  </si>
+  <si>
+    <t>Clear in DBS in 5*</t>
+  </si>
+  <si>
+    <t>Pune Fridge</t>
+  </si>
+  <si>
+    <t>Pune Washing Machine</t>
+  </si>
+  <si>
+    <t>take from Maa</t>
+  </si>
+  <si>
+    <t>as of 30DEC'22</t>
+  </si>
+  <si>
+    <t>GROWW</t>
+  </si>
+  <si>
+    <t>Closing Balance 04/07/21</t>
+  </si>
+  <si>
+    <t>Deposite Amount 31/07/21</t>
+  </si>
+  <si>
+    <t>Balance on 20/12/22</t>
+  </si>
+  <si>
+    <t>Closing Balance 31/12/22</t>
+  </si>
+  <si>
+    <t>Aditya Birla AMC</t>
+  </si>
+  <si>
+    <t>Short Term</t>
+  </si>
+  <si>
+    <t>Pure Saving (Bank/FD)</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>Needs(Home)</t>
+  </si>
+  <si>
+    <t>Wants(CAR EMI)</t>
+  </si>
+  <si>
+    <t>Future Allocation</t>
+  </si>
+  <si>
+    <t>paid as Rent</t>
+  </si>
+  <si>
+    <t>Papa Bank</t>
+  </si>
+  <si>
+    <t>Mom Bank</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>Latur Recharges(TV/ Wifi/ Mobile)</t>
+  </si>
+  <si>
+    <t>Pune Recharge(TV/ Wifi/ Mobile)</t>
+  </si>
+  <si>
+    <t>InCash(Milk+BC+RD+Bai)</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>[^ SHORT TERM SWITCH]</t>
+  </si>
+  <si>
+    <t>[# LONG TERM KEEP]</t>
+  </si>
+  <si>
+    <t>MF #</t>
+  </si>
+  <si>
+    <t>Max Life *#</t>
+  </si>
+  <si>
+    <t>Bajaj Life Goal *#</t>
+  </si>
+  <si>
+    <t>Indicators</t>
+  </si>
+  <si>
+    <t>Mid Term Savings</t>
+  </si>
+  <si>
+    <t>RD %</t>
+  </si>
+  <si>
+    <t>Car Debt Clear</t>
+  </si>
+  <si>
+    <t>iPhone Purchase Clear</t>
+  </si>
+  <si>
+    <t>Projected</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>% Allocation</t>
+  </si>
+  <si>
+    <t>Category for Allocation</t>
+  </si>
+  <si>
+    <t>Mirae Asset Tax Saver -3K[5th of Month][Start Aug'21][End Mar'23] | START NEW[Parag Parikh Tax Saver Fund Direct Growth]</t>
+  </si>
+  <si>
+    <t>Nippon Sensex - 2K[10th of Month][Start Aug'21][End Mar'23] | START NEW[HDFC Index S&amp;P BSE Sensex]</t>
+  </si>
+  <si>
+    <t>PGIM India Flexi Cap Fund Direct Growth - 2.5K[15th of Month][Start Jan'23]</t>
+  </si>
+  <si>
+    <t>Parag Parikh Flexi Cap [25th of Month][Start Aug'21][End Dec'22] | START NEW [Axis Small Cap]</t>
+  </si>
+  <si>
+    <t>PPF *#</t>
+  </si>
+  <si>
+    <t>[TODO] PPF</t>
+  </si>
+  <si>
+    <t>Sell - invest in ETFs</t>
+  </si>
+  <si>
+    <t>Term Life</t>
+  </si>
+  <si>
+    <t>Max Life</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Cover</t>
+  </si>
+  <si>
+    <t>Yearly Instalments</t>
+  </si>
+  <si>
+    <t>90 Lac</t>
+  </si>
+  <si>
+    <t>~9000</t>
+  </si>
+  <si>
+    <t>Life Goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajaj </t>
+  </si>
+  <si>
+    <t>On Maturity Return</t>
+  </si>
+  <si>
+    <t>3.96 Lac</t>
+  </si>
+  <si>
+    <t>Health Insurance</t>
+  </si>
+  <si>
+    <t>Tata AIG</t>
+  </si>
+  <si>
+    <t>[TODO]</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Sell - settle the Maa-A2</t>
+  </si>
+  <si>
+    <t>2: SECURE FUTURE</t>
+  </si>
+  <si>
+    <t>1: INVESTMENT PERFORMANCE</t>
+  </si>
+  <si>
+    <t>3: MBA [TODO]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4: RAISE MONEY </t>
+  </si>
+  <si>
+    <t>MOD Life</t>
+  </si>
+  <si>
+    <t>Parrotprince.com</t>
+  </si>
+  <si>
+    <t>Naya hai vaha YT channel</t>
+  </si>
+  <si>
+    <t>5: LOAN: CAR</t>
+  </si>
+  <si>
+    <t>Cutoff through Month(s)</t>
+  </si>
+  <si>
+    <t>as of 26DEC'22</t>
+  </si>
+  <si>
+    <t>% gain-&gt;</t>
+  </si>
+  <si>
+    <t>&lt;- invested total</t>
+  </si>
+  <si>
+    <t>&lt;- expected return</t>
+  </si>
+  <si>
+    <t>total return -&gt;</t>
+  </si>
+  <si>
+    <t>Disbursed Amount</t>
+  </si>
+  <si>
+    <t>Tenure</t>
+  </si>
+  <si>
+    <t>84 month</t>
+  </si>
+  <si>
+    <t>Outstanding (as of 26DEC'22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Interest </t>
+  </si>
+  <si>
+    <t>Interest Paid</t>
+  </si>
+  <si>
+    <t>Interest in Next Year</t>
+  </si>
+  <si>
+    <t>[^ 6months only - then merge to Home/InCash-DBS][Dec is last month]</t>
+  </si>
+  <si>
+    <t>as rent to Papa [Start Aug'22]</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1164,7 @@
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1157,8 +1258,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1195,8 +1348,54 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1275,11 +1474,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B050"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B050"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF00B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B050"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B050"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1389,13 +1619,137 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="40% - Accent1" xfId="3" builtinId="31"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1403,6 +1757,56 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="8"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1493,6 +1897,83 @@
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1645,34 +2126,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EAB1140C-4BE6-4DE4-93FB-AAF1DE17E19C}" name="ExtraEveryMonth" displayName="ExtraEveryMonth" ref="A27:H83" totalsRowShown="0" headerRowDxfId="19">
-  <autoFilter ref="A27:H83" xr:uid="{EAB1140C-4BE6-4DE4-93FB-AAF1DE17E19C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EAB1140C-4BE6-4DE4-93FB-AAF1DE17E19C}" name="ExtraEveryMonth" displayName="ExtraEveryMonth" ref="A27:H107" totalsRowShown="0" headerRowDxfId="42">
+  <autoFilter ref="A27:H107" xr:uid="{EAB1140C-4BE6-4DE4-93FB-AAF1DE17E19C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{9D94D9C6-B4DA-4545-A46C-4DC2768D6FD3}" name="Particular" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{9D94D9C6-B4DA-4545-A46C-4DC2768D6FD3}" name="Particular" dataDxfId="41"/>
     <tableColumn id="2" xr3:uid="{6717881D-2300-4D50-8806-3401BC619BFD}" name="Money"/>
     <tableColumn id="3" xr3:uid="{3F056D63-B00D-4759-B618-2694743A7532}" name="Payment from Bank"/>
-    <tableColumn id="4" xr3:uid="{44600B1F-E0B0-4FE8-AF63-B81966AEAFA2}" name="Settle from Bank" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{44600B1F-E0B0-4FE8-AF63-B81966AEAFA2}" name="Settle from Bank" dataDxfId="40"/>
     <tableColumn id="5" xr3:uid="{CA84091B-529F-42DD-AB6D-8C21002CC099}" name="Cause"/>
-    <tableColumn id="6" xr3:uid="{A06E4F07-8568-4FFE-A6DA-EED77A68A3DB}" name="Status" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{5A969EB3-F0B7-4795-9CE2-E15135959646}" name="Month" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{FF952BEA-5C19-415A-BE02-1324662D0DBE}" name="Comments" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{A06E4F07-8568-4FFE-A6DA-EED77A68A3DB}" name="Status" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{5A969EB3-F0B7-4795-9CE2-E15135959646}" name="Month" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{FF952BEA-5C19-415A-BE02-1324662D0DBE}" name="Comments" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7AD2728F-A954-4819-BCA1-42C6BB5AF3EF}" name="ExpenseTrack" displayName="ExpenseTrack" ref="A1:I25" totalsRowShown="0" headerRowDxfId="13">
-  <autoFilter ref="A1:I25" xr:uid="{7AD2728F-A954-4819-BCA1-42C6BB5AF3EF}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Not Done"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7AD2728F-A954-4819-BCA1-42C6BB5AF3EF}" name="ExpenseTrack" displayName="ExpenseTrack" ref="A1:I25" totalsRowShown="0" headerRowDxfId="36">
+  <autoFilter ref="A1:I25" xr:uid="{7AD2728F-A954-4819-BCA1-42C6BB5AF3EF}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{C54E3E68-D823-4633-B647-43E2D2EBE03D}" name="Particular"/>
-    <tableColumn id="2" xr3:uid="{9326109D-5E06-4604-829A-9DA6C9CE6C54}" name="Sub" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{9326109D-5E06-4604-829A-9DA6C9CE6C54}" name="Sub" dataDxfId="35"/>
     <tableColumn id="3" xr3:uid="{1530A0F3-9247-438C-A369-DF1F0765E081}" name="Rs"/>
     <tableColumn id="4" xr3:uid="{913C98B2-F355-488D-8E6F-3FDAC42510CA}" name="Bank"/>
     <tableColumn id="5" xr3:uid="{F84A3311-EE90-46A1-8DFC-B8DF66DD4F09}" name="Compromise"/>
@@ -1682,6 +2157,66 @@
     <tableColumn id="9" xr3:uid="{844651AC-E3C5-4216-897D-9746DA94157A}" name="Comments"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{344E1579-F105-42AD-B0A4-7BA3111ED67C}" name="Table1" displayName="Table1" ref="A6:E14" totalsRowShown="0" headerRowDxfId="34">
+  <autoFilter ref="A6:E14" xr:uid="{344E1579-F105-42AD-B0A4-7BA3111ED67C}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{F8E0C7D3-56D1-4413-9187-49343E711D78}" name="Rs"/>
+    <tableColumn id="2" xr3:uid="{8F92BBE9-4604-44FC-BE8A-4D8E776D167A}" name="Sector"/>
+    <tableColumn id="3" xr3:uid="{D4F8413C-8490-4EA1-9EA8-E0DD8E9C0639}" name="Mode"/>
+    <tableColumn id="4" xr3:uid="{53DAC18F-F68A-4943-8D20-23BD82B6917C}" name="Status"/>
+    <tableColumn id="5" xr3:uid="{178A2C75-8578-4076-A439-056A2F550CB3}" name="Actual Investment Declaration"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B2964901-5F4B-460B-926F-CE586CDB3E45}" name="Table4" displayName="Table4" ref="A17:F20" totalsRowShown="0" headerRowDxfId="33">
+  <autoFilter ref="A17:F20" xr:uid="{B2964901-5F4B-460B-926F-CE586CDB3E45}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{60D363DC-FD46-4441-A1C5-01E30F41BC37}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{9598BF18-7A67-4C5F-B772-BA1F8F53A116}" name="Category"/>
+    <tableColumn id="3" xr3:uid="{82D1F4FF-CE1B-400D-AD85-DD863436B553}" name="Unit"/>
+    <tableColumn id="4" xr3:uid="{C2047BBE-6156-4CFE-A49B-01C28454A890}" name="Current Amount"/>
+    <tableColumn id="5" xr3:uid="{8DDEE30A-D956-4505-9BCB-0715700C3B1C}" name="Invested Amount"/>
+    <tableColumn id="6" xr3:uid="{04422BDD-30AB-4E5D-9F3F-44A284537165}" name="Platform"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{48145BB3-112E-4B93-9F0C-579C10D81536}" name="Table5" displayName="Table5" ref="A21:G33" totalsRowShown="0" headerRowDxfId="32">
+  <autoFilter ref="A21:G33" xr:uid="{48145BB3-112E-4B93-9F0C-579C10D81536}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{5C3AC751-65B8-4FB0-BF62-2EC169180B78}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{CE2081DF-D584-44D4-8E6B-609F00D0302F}" name="Category"/>
+    <tableColumn id="3" xr3:uid="{7C1076FB-337B-436E-8054-4185698C5317}" name="Unit"/>
+    <tableColumn id="4" xr3:uid="{8F193749-F741-43A8-87E9-08C58E219F2A}" name="Current Amount"/>
+    <tableColumn id="5" xr3:uid="{A3E9F02B-13C0-4F0D-B617-C3B47C57AC31}" name="Invested Amount"/>
+    <tableColumn id="6" xr3:uid="{2B820C61-C0EA-4FD7-8452-03A811431FC2}" name="Platform"/>
+    <tableColumn id="7" xr3:uid="{2D07516C-064C-4570-A722-153D8F0663DB}" name="Plan of Action"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7CF78C27-E549-42DF-8144-BD35382538CA}" name="Table6" displayName="Table6" ref="A38:F41" totalsRowShown="0">
+  <autoFilter ref="A38:F41" xr:uid="{7CF78C27-E549-42DF-8144-BD35382538CA}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{D503695C-52D1-41D3-A551-944D04A34F1A}" name="Type"/>
+    <tableColumn id="2" xr3:uid="{8A08AFDD-FC93-41D3-BAE2-5B3F5AD27667}" name="Company"/>
+    <tableColumn id="3" xr3:uid="{8D66F48F-10A8-469E-AD52-9A35E60DF2F6}" name="Cover"/>
+    <tableColumn id="4" xr3:uid="{DC1B289B-D2C5-4BFE-93AF-104DC55C702E}" name="Yearly Instalments" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{166F9D1C-E25C-4771-A30C-011F7FB8B3BF}" name="On Maturity Return"/>
+    <tableColumn id="6" xr3:uid="{BDE94F5D-C23E-4033-9CDD-1612F612E90B}" name="Comments"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1982,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB43EA2E-854B-41C1-8819-79EEB1896E8C}">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
@@ -1997,7 +2532,7 @@
     <col min="10" max="10" width="7.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>17</v>
       </c>
@@ -2011,7 +2546,7 @@
         <v>19</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F1" s="31" t="s">
         <v>21</v>
@@ -2023,10 +2558,10 @@
         <v>31</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
@@ -2040,24 +2575,24 @@
         <v>4</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="C3" s="12">
         <v>2000</v>
@@ -2066,22 +2601,22 @@
         <v>5</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H3">
         <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>0</v>
       </c>
@@ -2089,28 +2624,28 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="33" t="s">
         <v>0</v>
       </c>
@@ -2118,25 +2653,25 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="33" t="s">
         <v>0</v>
       </c>
@@ -2150,10 +2685,10 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -2162,10 +2697,10 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
         <v>0</v>
       </c>
@@ -2179,10 +2714,10 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G7" t="s">
         <v>29</v>
@@ -2191,10 +2726,10 @@
         <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="33" t="s">
         <v>0</v>
       </c>
@@ -2208,10 +2743,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -2220,10 +2755,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="33" t="s">
         <v>0</v>
       </c>
@@ -2237,10 +2772,10 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
@@ -2249,10 +2784,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
         <v>0</v>
       </c>
@@ -2266,19 +2801,16 @@
         <v>5</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
       </c>
-      <c r="J10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>0</v>
       </c>
@@ -2292,27 +2824,21 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F11" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
       </c>
-      <c r="J11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="38" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="C12">
         <v>2501</v>
@@ -2321,22 +2847,22 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H12">
         <v>10</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="35" t="s">
         <v>9</v>
       </c>
@@ -2350,22 +2876,22 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>9</v>
       </c>
@@ -2379,24 +2905,24 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C15">
         <v>3300</v>
@@ -2405,22 +2931,22 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="42" t="s">
         <v>22</v>
       </c>
@@ -2434,13 +2960,13 @@
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16">
         <v>8</v>
@@ -2451,7 +2977,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="C17">
         <v>3800</v>
@@ -2460,7 +2986,7 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -2472,15 +2998,15 @@
         <v>8</v>
       </c>
       <c r="I17" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="C18">
         <v>3000</v>
@@ -2489,24 +3015,24 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H18">
         <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>2</v>
@@ -2518,22 +3044,22 @@
         <v>14</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H19" s="11"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C20">
         <v>5002</v>
@@ -2542,24 +3068,24 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H20">
         <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>10</v>
@@ -2571,23 +3097,23 @@
         <v>14</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C22">
         <v>800</v>
@@ -2596,24 +3122,24 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>32</v>
@@ -2625,19 +3151,19 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2653,7 +3179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -2661,7 +3187,7 @@
     </row>
     <row r="26" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="30" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="1"/>
@@ -2674,30 +3200,30 @@
         <v>17</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="27" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B28">
         <v>600</v>
@@ -2706,13 +3232,13 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -2725,27 +3251,27 @@
         <v>7609</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s">
         <v>29</v>
       </c>
       <c r="G29" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="27" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B30">
         <v>3300</v>
@@ -2757,19 +3283,19 @@
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="27" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B31">
         <v>1500</v>
@@ -2781,19 +3307,19 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="27" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B32">
         <v>4000</v>
@@ -2808,16 +3334,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="27" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B33">
         <v>1220</v>
@@ -2829,13 +3355,13 @@
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F33" t="s">
         <v>29</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -2850,24 +3376,24 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E34" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F34" t="s">
         <v>29</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="27" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B35">
         <v>3420</v>
@@ -2879,13 +3405,13 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F35" t="s">
         <v>29</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -2897,55 +3423,55 @@
         <v>4439.78</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="27" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B37">
         <v>1953</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="F37" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J37" s="15"/>
       <c r="K37" s="16"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="27" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B38">
         <v>3000</v>
@@ -2957,19 +3483,19 @@
         <v>5</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H38" s="25"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B39" s="9">
         <v>2500</v>
@@ -2981,19 +3507,19 @@
         <v>5</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="27" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B40" s="9">
         <v>4800</v>
@@ -3005,19 +3531,19 @@
         <v>5</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="B41" s="9">
         <v>9744.75</v>
@@ -3029,21 +3555,21 @@
         <v>5</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B42" s="9">
         <v>2200</v>
@@ -3055,19 +3581,19 @@
         <v>5</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="28" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B43" s="9">
         <v>730</v>
@@ -3079,19 +3605,19 @@
         <v>5</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="28" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B44" s="9">
         <v>250</v>
@@ -3103,19 +3629,19 @@
         <v>5</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B45" s="9">
         <v>700</v>
@@ -3124,21 +3650,21 @@
         <v>14</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>29</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="27" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B46" s="9">
         <v>1350</v>
@@ -3150,13 +3676,13 @@
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H46" s="10"/>
       <c r="J46">
@@ -3165,29 +3691,29 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="27" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B47" s="9">
         <f>2500+1000</f>
         <v>3500</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D47" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="J47">
         <v>755</v>
@@ -3195,60 +3721,60 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B48" s="9">
         <f>1000+500</f>
         <v>1500</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="27" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B49" s="9">
         <v>699</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B50" s="9">
         <f>155+350+150</f>
@@ -3261,46 +3787,46 @@
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="27" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B51" s="9">
         <f>488</f>
         <v>488</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D51" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="27" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B52" s="9">
         <f>375+1150+480+280+40+190</f>
@@ -3313,19 +3839,19 @@
         <v>5</v>
       </c>
       <c r="E52" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="27" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B53" s="9">
         <f>2000+556+75</f>
@@ -3338,19 +3864,19 @@
         <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="27" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B54">
         <f>1529-450</f>
@@ -3363,70 +3889,70 @@
         <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="27" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B55">
         <f>1400+750</f>
         <v>2150</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="27" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="B56">
         <v>13759</v>
       </c>
       <c r="C56" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H56" s="26" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="27" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B57">
         <f>2000+460+800</f>
@@ -3439,13 +3965,13 @@
         <v>14</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>29</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H57" s="10"/>
     </row>
@@ -3457,27 +3983,27 @@
         <v>1087</v>
       </c>
       <c r="C58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D58" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="27" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="B59" s="9">
         <v>1330</v>
@@ -3489,19 +4015,19 @@
         <v>4</v>
       </c>
       <c r="E59" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H59" s="10"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="27" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B60" s="9">
         <v>580</v>
@@ -3513,122 +4039,122 @@
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H60" s="10"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="27" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B61">
         <v>1078</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H61" s="10"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="27" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B62">
         <v>69900</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D62" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="H62" s="26" t="s">
-        <v>163</v>
+        <v>118</v>
+      </c>
+      <c r="H62" s="68" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="27" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="B63">
         <v>10850</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D63" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="27" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="B64">
         <f>464+250</f>
         <v>714</v>
       </c>
       <c r="C64" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D64" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E64" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="27" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="B65">
         <v>1430</v>
@@ -3640,13 +4166,13 @@
         <v>4</v>
       </c>
       <c r="E65" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="H65" s="10"/>
     </row>
@@ -3658,27 +4184,27 @@
         <v>2020</v>
       </c>
       <c r="C66" s="46" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D66" s="47" t="s">
         <v>5</v>
       </c>
       <c r="E66" s="48" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F66" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="45" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="B67" s="46">
         <f>115+120+350+450+850+130</f>
@@ -3691,19 +4217,19 @@
         <v>4</v>
       </c>
       <c r="E67" s="46" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F67" s="49" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G67" s="47" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="H67" s="50"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="45" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="B68" s="46">
         <f>2425+80+55</f>
@@ -3716,74 +4242,74 @@
         <v>5</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F68" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G68" s="47" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="45" t="s">
-        <v>283</v>
+        <v>237</v>
       </c>
       <c r="B69" s="46">
         <f>670*3</f>
         <v>2010</v>
       </c>
       <c r="C69" s="46" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D69" s="47" t="s">
         <v>5</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F69" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G69" s="47" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="53" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="B70" s="46">
         <v>2000</v>
       </c>
       <c r="C70" s="46" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D70" s="47" t="s">
         <v>4</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F70" s="49" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G70" s="47" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="53" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="B71" s="46">
         <v>2413</v>
@@ -3795,42 +4321,42 @@
         <v>5</v>
       </c>
       <c r="E71" s="46" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F71" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G71" s="47" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="H71" s="50" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="53" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="B72" s="46">
         <v>3005</v>
       </c>
       <c r="C72" s="46" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D72" s="47" t="s">
         <v>5</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F72" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G72" s="47" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="H72" s="50" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
@@ -3841,53 +4367,53 @@
         <v>4500</v>
       </c>
       <c r="C73" s="46" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D73" s="47" t="s">
         <v>5</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F73" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="53" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="B74" s="46">
         <v>3500</v>
       </c>
       <c r="C74" s="46" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D74" s="47" t="s">
         <v>5</v>
       </c>
       <c r="E74" s="55" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F74" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G74" s="47" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="H74" s="50" t="s">
-        <v>305</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="27" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="B75" s="46">
         <v>800</v>
@@ -3899,152 +4425,152 @@
         <v>4</v>
       </c>
       <c r="E75" s="55" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F75" s="49" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G75" s="47" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>310</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="57" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="B76" s="58">
         <v>3500</v>
       </c>
       <c r="C76" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D76" s="59" t="s">
         <v>5</v>
       </c>
       <c r="E76" s="60" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F76" s="58" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="G76" s="59" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="H76" s="61" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="57" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="B77" s="58">
         <v>3500</v>
       </c>
       <c r="C77" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D77" s="59" t="s">
         <v>5</v>
       </c>
       <c r="E77" s="60" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F77" s="58" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="G77" s="59" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="H77" s="61" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="57" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="B78" s="58">
         <v>3500</v>
       </c>
       <c r="C78" s="58" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D78" s="59" t="s">
         <v>5</v>
       </c>
       <c r="E78" s="60" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F78" s="58" t="s">
         <v>29</v>
       </c>
       <c r="G78" s="59" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H78" s="61" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="B79" s="46">
-        <v>2700</v>
-      </c>
-      <c r="C79" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="D79" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="E79" s="55" t="s">
-        <v>165</v>
-      </c>
-      <c r="F79" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="G79" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="H79" s="50"/>
+      <c r="A79" s="57" t="s">
+        <v>255</v>
+      </c>
+      <c r="B79" s="58">
+        <v>3500</v>
+      </c>
+      <c r="C79" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="D79" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="E79" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="F79" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G79" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H79" s="61" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="53" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="B80" s="46">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="C80" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="D80" s="56" t="s">
         <v>4</v>
       </c>
+      <c r="D80" s="47" t="s">
+        <v>4</v>
+      </c>
       <c r="E80" s="55" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="F80" s="49" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G80" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="H80" s="50" t="s">
-        <v>314</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="H80" s="50"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="53" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="B81" s="46">
-        <v>480</v>
+        <v>2600</v>
       </c>
       <c r="C81" s="46" t="s">
         <v>27</v>
@@ -4053,116 +4579,595 @@
         <v>4</v>
       </c>
       <c r="E81" s="55" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="F81" s="49" t="s">
         <v>29</v>
       </c>
       <c r="G81" s="47" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="H81" s="50" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="53" t="s">
-        <v>315</v>
+        <v>267</v>
       </c>
       <c r="B82" s="46">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="C82" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="D82" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="E82" s="46" t="s">
-        <v>165</v>
+        <v>27</v>
+      </c>
+      <c r="D82" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E82" s="55" t="s">
+        <v>131</v>
       </c>
       <c r="F82" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="G82" s="62" t="s">
-        <v>302</v>
+      <c r="G82" s="47" t="s">
+        <v>256</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="53" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="B83" s="46">
+        <v>460</v>
+      </c>
+      <c r="C83" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D83" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F83" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83" s="62" t="s">
+        <v>256</v>
+      </c>
+      <c r="H83" s="50" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="B84" s="46">
+        <v>1000</v>
+      </c>
+      <c r="C84" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E84" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F84" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G84" s="62" t="s">
+        <v>257</v>
+      </c>
+      <c r="H84" s="50"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="53" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" s="46">
         <v>2500</v>
       </c>
-      <c r="C83" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="F83" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="G83" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="H83" s="50"/>
+      <c r="C85" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F85" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G85" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="H85" s="50"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="B86" s="46">
+        <f>2317+2396+2398</f>
+        <v>7111</v>
+      </c>
+      <c r="C86" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D86" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F86" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G86" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="H86" s="50" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="53" t="s">
+        <v>274</v>
+      </c>
+      <c r="B87" s="46">
+        <v>2000</v>
+      </c>
+      <c r="C87" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E87" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F87" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G87" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="H87" s="50" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="B88" s="46">
+        <f>1800+1000+800</f>
+        <v>3600</v>
+      </c>
+      <c r="C88" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E88" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F88" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G88" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="H88" s="50" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="53" t="s">
+        <v>277</v>
+      </c>
+      <c r="B89" s="46">
+        <v>1300</v>
+      </c>
+      <c r="C89" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F89" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G89" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="H89" s="50"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="B90" s="46">
+        <v>5500</v>
+      </c>
+      <c r="C90" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E90" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F90" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G90" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H90" s="64" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="46">
+        <v>3500</v>
+      </c>
+      <c r="C91" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D91" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F91" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G91" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H91" s="50"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="53" t="s">
+        <v>280</v>
+      </c>
+      <c r="B92" s="46">
+        <v>500</v>
+      </c>
+      <c r="C92" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E92" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F92" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G92" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H92" s="50"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="B93" s="46">
+        <f>350+450+659</f>
+        <v>1459</v>
+      </c>
+      <c r="C93" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E93" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F93" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G93" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H93" s="50"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="B94" s="46">
+        <v>3730</v>
+      </c>
+      <c r="C94" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F94" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G94" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H94" s="50" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B95" s="46">
+        <v>400</v>
+      </c>
+      <c r="C95" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E95" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F95" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G95" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H95" s="50"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="B96" s="46">
+        <v>30000</v>
+      </c>
+      <c r="C96" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F96" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="G96" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H96" s="64"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="B97" s="46">
+        <v>17000</v>
+      </c>
+      <c r="C97" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E97" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F97" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G97" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H97" s="64" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" s="27"/>
+      <c r="B98" s="46"/>
+      <c r="C98" s="46"/>
+      <c r="D98" s="47"/>
+      <c r="E98" s="46"/>
+      <c r="F98" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="G98" s="47"/>
+      <c r="H98" s="50"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" s="27"/>
+      <c r="B99" s="46"/>
+      <c r="C99" s="46"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="46"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="50"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" s="27"/>
+      <c r="B100" s="46"/>
+      <c r="C100" s="46"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="46"/>
+      <c r="F100" s="49"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="50"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101" s="27"/>
+      <c r="B101" s="46"/>
+      <c r="C101" s="46"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="46"/>
+      <c r="F101" s="49"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="50"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102" s="27"/>
+      <c r="B102" s="46"/>
+      <c r="C102" s="46"/>
+      <c r="D102" s="47"/>
+      <c r="E102" s="46"/>
+      <c r="F102" s="49"/>
+      <c r="G102" s="47"/>
+      <c r="H102" s="50"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" s="27"/>
+      <c r="B103" s="46"/>
+      <c r="C103" s="46"/>
+      <c r="D103" s="47"/>
+      <c r="E103" s="46"/>
+      <c r="F103" s="49"/>
+      <c r="G103" s="47"/>
+      <c r="H103" s="50"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104" s="27"/>
+      <c r="B104" s="46"/>
+      <c r="C104" s="46"/>
+      <c r="D104" s="47"/>
+      <c r="E104" s="46"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="47"/>
+      <c r="H104" s="50"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105" s="27"/>
+      <c r="B105" s="46"/>
+      <c r="C105" s="46"/>
+      <c r="D105" s="47"/>
+      <c r="E105" s="46"/>
+      <c r="F105" s="49"/>
+      <c r="G105" s="47"/>
+      <c r="H105" s="50"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106" s="27"/>
+      <c r="B106" s="46"/>
+      <c r="C106" s="46"/>
+      <c r="D106" s="47"/>
+      <c r="E106" s="46"/>
+      <c r="F106" s="49"/>
+      <c r="G106" s="47"/>
+      <c r="H106" s="50"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" s="27"/>
+      <c r="B107" s="46"/>
+      <c r="C107" s="46"/>
+      <c r="D107" s="47"/>
+      <c r="E107" s="46"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="47"/>
+      <c r="H107" s="50"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E36:E37 H36:H37 H34 F84:F1048576 G70 F69:F70 H63 G1:I1 E27:E29 H27 F27:G37 F1:F26 E40:E42 E44:E60 F38:F64">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="INVEST">
+  <conditionalFormatting sqref="E36:E37 H36:H37 H34 G70 F69:F70 H63 G1:I1 E27:E29 H27 F27:G37 F1:F26 E40:E42 E44:E60 F38:F64 F86:F1048576">
+    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="INVEST">
       <formula>NOT(ISERROR(SEARCH("INVEST",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E35:E37 F84:F1048576 G70 F69:F70 E27:E30 F1:F26 E40:E42 E44:E60">
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="Debt">
+  <conditionalFormatting sqref="E35:E37 G70 F69:F70 E27:E30 F1:F26 E40:E42 E44:E60 F86:F1048576">
+    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="Debt">
       <formula>NOT(ISERROR(SEARCH("Debt",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61:E62">
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="INVEST">
+    <cfRule type="containsText" dxfId="26" priority="14" operator="containsText" text="INVEST">
       <formula>NOT(ISERROR(SEARCH("INVEST",E61)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61:E62">
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Debt">
+    <cfRule type="containsText" dxfId="25" priority="15" operator="containsText" text="Debt">
       <formula>NOT(ISERROR(SEARCH("Debt",E61)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E27:E91">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+  <conditionalFormatting sqref="E27:E77 E79:E107">
+    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
       <formula>"NEED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
       <formula>"DEBT"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28:E83">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+  <conditionalFormatting sqref="E28:E77 E79:E107">
+    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
       <formula>"WANTS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F83">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+  <conditionalFormatting sqref="F28:F77 F79:F107">
+    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
       <formula>"LIB"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="9" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
       <formula>"Not Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F25">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
       <formula>"W/N"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E78">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+      <formula>"NEED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+      <formula>"DEBT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E78">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+      <formula>"WANTS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F78">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+      <formula>"LIB"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+      <formula>"Not Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4175,1133 +5180,317 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7DD2E2-FF1A-4BB9-A01E-B2195D3FEF92}">
-  <dimension ref="A2:N55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC598DA-2729-43AC-A491-449281604C2E}">
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="36.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="28.1796875" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>22.42</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" t="s">
-        <v>230</v>
-      </c>
-      <c r="I2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>17.7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F3" s="32">
-        <v>58297</v>
-      </c>
-      <c r="I3" s="32">
-        <f>F3-F16</f>
-        <v>55141</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" t="s">
-        <v>247</v>
-      </c>
-      <c r="M3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>22.42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K4" t="s">
-        <v>249</v>
-      </c>
-      <c r="L4" s="32">
-        <v>504209</v>
-      </c>
-      <c r="M4" s="32">
-        <v>657620</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>20.6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>129</v>
-      </c>
-      <c r="K5" t="s">
-        <v>250</v>
-      </c>
-      <c r="L5" s="32">
-        <v>13876</v>
-      </c>
-      <c r="M5" s="32">
-        <v>29392</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>9.44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" t="s">
-        <v>231</v>
-      </c>
-      <c r="G6" t="s">
-        <v>232</v>
-      </c>
-      <c r="K6" t="s">
-        <v>251</v>
-      </c>
-      <c r="L6" s="32">
-        <v>9252</v>
-      </c>
-      <c r="M6" s="32">
-        <v>24768</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1">
+        <v>8705</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B2">
+        <f>101800+15710</f>
+        <v>117510</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B3">
+        <v>30400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>11.8</v>
+        <v>3000</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" t="s">
-        <v>233</v>
-      </c>
-      <c r="G7">
-        <v>24038</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>22.42</v>
+        <v>30000</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" t="s">
-        <v>234</v>
-      </c>
-      <c r="G8">
-        <v>9615</v>
-      </c>
-      <c r="K8" t="s">
-        <v>252</v>
-      </c>
-      <c r="L8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>22.42</v>
+        <v>13800</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" t="s">
-        <v>235</v>
-      </c>
-      <c r="G9">
-        <v>200</v>
-      </c>
-      <c r="J9" t="s">
-        <v>272</v>
-      </c>
-      <c r="K9" t="s">
-        <v>253</v>
-      </c>
-      <c r="L9">
-        <v>605221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>22.42</v>
+        <v>10000</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" t="s">
-        <v>236</v>
-      </c>
-      <c r="G10">
-        <v>1500</v>
-      </c>
-      <c r="J10" t="s">
-        <v>272</v>
-      </c>
-      <c r="K10" t="s">
-        <v>267</v>
-      </c>
-      <c r="L10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>0.11</v>
+        <v>20000</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11">
-        <v>3000</v>
-      </c>
-      <c r="J11" t="s">
-        <v>272</v>
-      </c>
-      <c r="K11" t="s">
-        <v>254</v>
-      </c>
-      <c r="L11">
-        <v>21600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>0.88</v>
+        <v>5000</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" t="s">
-        <v>238</v>
-      </c>
-      <c r="G12">
-        <v>18444</v>
-      </c>
-      <c r="J12" t="s">
-        <v>272</v>
-      </c>
-      <c r="K12" t="s">
-        <v>255</v>
-      </c>
-      <c r="L12">
-        <v>48414</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>4.72</v>
+        <v>14000</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" t="s">
-        <v>239</v>
-      </c>
-      <c r="G13">
-        <v>1500</v>
-      </c>
-      <c r="J13" t="s">
-        <v>272</v>
-      </c>
-      <c r="K13" t="s">
-        <v>256</v>
-      </c>
-      <c r="L13">
-        <v>30998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>2.36</v>
+        <v>21000</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="K14" s="44" t="s">
-        <v>269</v>
-      </c>
-      <c r="L14" s="44"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>0.11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>139</v>
-      </c>
-      <c r="F15" t="s">
-        <v>240</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="K15" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="L15" s="44">
-        <f>8*3000</f>
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>0.11</v>
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="32">
-        <v>3156</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="K16" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="L16" s="44">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>22.42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>140</v>
-      </c>
-      <c r="J17" t="s">
-        <v>272</v>
-      </c>
-      <c r="K17" t="s">
-        <v>257</v>
-      </c>
-      <c r="L17">
-        <v>504210</v>
-      </c>
-      <c r="M17">
-        <f>L18-12500</f>
-        <v>842</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="J18" t="s">
-        <v>272</v>
-      </c>
-      <c r="K18" t="s">
-        <v>258</v>
-      </c>
-      <c r="L18">
-        <v>13342</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="F17" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="63">
+        <f>24999-650</f>
+        <v>24349</v>
+      </c>
+      <c r="E18">
+        <v>24999</v>
+      </c>
+      <c r="F18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="63">
+        <f>+E19-15725</f>
+        <v>55055</v>
+      </c>
+      <c r="E19">
+        <v>70780</v>
+      </c>
       <c r="F19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G19" t="s">
-        <v>232</v>
-      </c>
-      <c r="J19" t="s">
-        <v>272</v>
-      </c>
-      <c r="K19" t="s">
-        <v>259</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="2">
+        <v>21731</v>
+      </c>
+      <c r="E20">
+        <v>21731</v>
+      </c>
       <c r="F20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G20">
-        <v>1800</v>
-      </c>
-      <c r="J20" t="s">
-        <v>272</v>
-      </c>
-      <c r="K20" t="s">
-        <v>260</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F21" t="s">
-        <v>243</v>
-      </c>
-      <c r="G21">
-        <v>200</v>
-      </c>
-      <c r="J21" t="s">
-        <v>272</v>
-      </c>
-      <c r="K21" t="s">
-        <v>261</v>
-      </c>
-      <c r="L21">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F22" t="s">
-        <v>244</v>
-      </c>
-      <c r="G22">
-        <v>1156</v>
-      </c>
-      <c r="J22" t="s">
-        <v>272</v>
-      </c>
-      <c r="K22" t="s">
-        <v>262</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="J23" t="s">
-        <v>272</v>
-      </c>
-      <c r="K23" t="s">
-        <v>263</v>
-      </c>
-      <c r="L23">
-        <v>13876</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K24" t="s">
-        <v>264</v>
-      </c>
-      <c r="L24">
-        <v>4624</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K25" t="s">
-        <v>265</v>
-      </c>
-      <c r="L25">
-        <v>9252</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K26" t="s">
-        <v>266</v>
-      </c>
-      <c r="L26">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
-        <v>297</v>
-      </c>
-      <c r="C29" s="54">
-        <v>24038</v>
-      </c>
-      <c r="D29" s="54">
-        <v>288456</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>298</v>
-      </c>
-      <c r="C30" s="54">
-        <v>9615</v>
-      </c>
-      <c r="D30" s="54">
-        <v>115380</v>
-      </c>
-      <c r="E30" s="14">
-        <f>D30*100/D29</f>
-        <v>39.999167984025291</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>293</v>
-      </c>
-      <c r="C31">
-        <v>200</v>
-      </c>
-      <c r="D31" s="54">
-        <v>2400</v>
-      </c>
-      <c r="E31" s="14">
-        <f>D31*100/D29</f>
-        <v>0.8320159747067144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
-        <v>294</v>
-      </c>
-      <c r="C32" s="54">
-        <v>1500</v>
-      </c>
-      <c r="D32" s="54">
-        <v>18000</v>
-      </c>
-      <c r="E32" s="14">
-        <f>D32*100/D29</f>
-        <v>6.2401198103003575</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
-        <v>299</v>
-      </c>
-      <c r="C33" s="54">
-        <v>3000</v>
-      </c>
-      <c r="D33" s="54">
-        <v>36000</v>
-      </c>
-      <c r="E33" s="14">
-        <f>D33*100/D29</f>
-        <v>12.480239620600715</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B34" t="s">
-        <v>295</v>
-      </c>
-      <c r="C34" s="54">
-        <v>1500</v>
-      </c>
-      <c r="D34" s="54">
-        <v>18000</v>
-      </c>
-      <c r="E34" s="14">
-        <f>D34*100/D29</f>
-        <v>6.2401198103003575</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B35" t="s">
-        <v>296</v>
-      </c>
-      <c r="C35" s="54">
-        <v>18444</v>
-      </c>
-      <c r="D35" s="54">
-        <v>221328</v>
-      </c>
-      <c r="E35" s="14">
-        <f>D35*100/D29</f>
-        <v>76.728513187453203</v>
-      </c>
-    </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>300</v>
-      </c>
-      <c r="C36" s="54">
-        <f>SUM(C30:C35)</f>
-        <v>34259</v>
-      </c>
-      <c r="D36" s="54">
-        <f>SUM(D30:D35)</f>
-        <v>411108</v>
-      </c>
-      <c r="E36" s="14">
-        <f>D36*100/D29</f>
-        <v>142.52017638738664</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C42" s="21"/>
-      <c r="D42" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="J42" t="s">
-        <v>323</v>
-      </c>
-      <c r="K42" t="s">
-        <v>152</v>
-      </c>
-      <c r="L42" t="s">
-        <v>153</v>
-      </c>
-      <c r="M42" t="s">
-        <v>156</v>
-      </c>
-      <c r="N42" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C43" s="21"/>
-      <c r="D43" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21">
-        <v>1</v>
-      </c>
-      <c r="J43" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K43" s="22">
-        <v>6748</v>
-      </c>
-      <c r="L43">
-        <v>743</v>
-      </c>
-      <c r="M43" s="22">
-        <f>L43*0.18</f>
-        <v>133.74</v>
-      </c>
-      <c r="N43" s="22">
-        <v>56901</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C44" s="21"/>
-      <c r="D44" s="21">
-        <f>95200/12+5000</f>
-        <v>12933.333333333332</v>
-      </c>
-      <c r="E44" s="64" t="s">
-        <v>319</v>
-      </c>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21">
-        <v>2</v>
-      </c>
-      <c r="J44" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K44" s="22">
-        <v>6827</v>
-      </c>
-      <c r="L44">
-        <v>664</v>
-      </c>
-      <c r="M44" s="22">
-        <f t="shared" ref="M44:M51" si="0">L44*0.18</f>
-        <v>119.52</v>
-      </c>
-      <c r="N44" s="22">
-        <v>50073</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C45" s="21"/>
-      <c r="D45" s="21">
-        <f>(1360000/12)-D44</f>
-        <v>100400</v>
-      </c>
-      <c r="E45" s="64" t="s">
-        <v>320</v>
-      </c>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21">
-        <v>3</v>
-      </c>
-      <c r="J45" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K45" s="22">
-        <v>6907</v>
-      </c>
-      <c r="L45">
-        <v>584</v>
-      </c>
-      <c r="M45" s="22">
-        <f t="shared" si="0"/>
-        <v>105.11999999999999</v>
-      </c>
-      <c r="N45" s="22">
-        <v>43167</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C46" s="21"/>
-      <c r="D46" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21">
-        <v>4</v>
-      </c>
-      <c r="J46" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K46" s="22">
-        <v>6987</v>
-      </c>
-      <c r="L46">
-        <v>504</v>
-      </c>
-      <c r="M46" s="22">
-        <f t="shared" si="0"/>
-        <v>90.72</v>
-      </c>
-      <c r="N46" s="22">
-        <v>36179</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C47" s="21"/>
-      <c r="D47" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="E47" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21">
-        <v>5</v>
-      </c>
-      <c r="J47" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K47" s="22">
-        <v>7069</v>
-      </c>
-      <c r="L47">
-        <v>422</v>
-      </c>
-      <c r="M47" s="22">
-        <f t="shared" si="0"/>
-        <v>75.959999999999994</v>
-      </c>
-      <c r="N47" s="22">
-        <v>29110</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21">
-        <v>6</v>
-      </c>
-      <c r="J48" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K48" s="22">
-        <v>7151</v>
-      </c>
-      <c r="L48">
-        <v>340</v>
-      </c>
-      <c r="M48" s="22">
-        <f t="shared" si="0"/>
-        <v>61.199999999999996</v>
-      </c>
-      <c r="N48" s="22">
-        <v>21959</v>
-      </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21">
-        <v>7</v>
-      </c>
-      <c r="J49" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K49" s="22">
-        <v>7235</v>
-      </c>
-      <c r="L49">
-        <v>256</v>
-      </c>
-      <c r="M49" s="22">
-        <f t="shared" si="0"/>
-        <v>46.08</v>
-      </c>
-      <c r="N49" s="22">
-        <v>14724</v>
-      </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21">
-        <v>8</v>
-      </c>
-      <c r="J50" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K50" s="22">
-        <v>7319</v>
-      </c>
-      <c r="L50">
-        <v>172</v>
-      </c>
-      <c r="M50" s="22">
-        <f t="shared" si="0"/>
-        <v>30.959999999999997</v>
-      </c>
-      <c r="N50" s="22">
-        <v>7405</v>
-      </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21">
-        <v>9</v>
-      </c>
-      <c r="J51" s="22">
-        <v>7492</v>
-      </c>
-      <c r="K51" s="22">
-        <v>7405</v>
-      </c>
-      <c r="L51">
-        <v>86</v>
-      </c>
-      <c r="M51" s="22">
-        <f t="shared" si="0"/>
-        <v>15.479999999999999</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="22"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="I53" s="22"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="I54" s="22"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="L55" s="22"/>
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC598DA-2729-43AC-A491-449281604C2E}">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02AFA30-1EFA-4C67-A054-A88F37796921}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>10000</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>30000</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>13800</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>10000</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>20000</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>5000</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>14000</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>11000</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D9" xr:uid="{9627EC86-74FD-451D-8808-19D38708C253}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02AFA30-1EFA-4C67-A054-A88F37796921}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.36328125" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" customWidth="1"/>
+    <col min="7" max="7" width="21.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.08984375" customWidth="1"/>
     <col min="16" max="16" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>179</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -5318,70 +5507,70 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C3">
-        <v>6290</v>
+        <v>7927</v>
       </c>
       <c r="D3">
-        <v>455</v>
+        <v>2375</v>
       </c>
       <c r="E3">
-        <v>10902</v>
+        <v>8442</v>
       </c>
       <c r="F3">
-        <v>55383</v>
+        <v>56297</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C4">
-        <v>15241</v>
+        <v>21603</v>
       </c>
       <c r="D4">
-        <v>3041</v>
+        <v>3052</v>
       </c>
       <c r="E4">
-        <v>8453</v>
+        <v>9859</v>
       </c>
       <c r="F4">
-        <v>8828</v>
+        <v>14507</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C5">
-        <v>7927</v>
+        <v>13705</v>
       </c>
       <c r="D5">
-        <v>2785</v>
+        <v>652</v>
       </c>
       <c r="E5">
-        <v>8345</v>
+        <v>6233</v>
       </c>
       <c r="F5">
-        <v>1156</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>14</v>
@@ -5395,99 +5584,93 @@
       <c r="F8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="22"/>
       <c r="P8" s="22"/>
       <c r="S8" s="22"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C9">
-        <v>7927</v>
+        <v>13705</v>
       </c>
       <c r="D9">
-        <v>2375</v>
+        <v>652</v>
       </c>
       <c r="E9">
-        <v>8442</v>
+        <v>6233</v>
       </c>
       <c r="F9">
-        <v>56297</v>
-      </c>
-      <c r="O9" s="22"/>
+        <v>82278</v>
+      </c>
       <c r="P9" s="22"/>
       <c r="S9" s="22"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C10">
-        <v>21603</v>
+        <v>24623</v>
       </c>
       <c r="D10">
-        <v>3052</v>
+        <v>1603</v>
       </c>
       <c r="E10">
-        <v>9859</v>
+        <v>7233</v>
       </c>
       <c r="F10">
-        <v>14507</v>
+        <v>37672</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10" s="22"/>
+        <v>45</v>
+      </c>
       <c r="P10" s="22"/>
       <c r="S10" s="22"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C11">
-        <v>13705</v>
+        <v>11822</v>
       </c>
       <c r="D11">
-        <v>652</v>
+        <v>1603</v>
       </c>
       <c r="E11">
-        <v>6233</v>
+        <v>5168</v>
       </c>
       <c r="F11">
-        <v>66</v>
-      </c>
-      <c r="O11" s="22"/>
+        <v>478</v>
+      </c>
       <c r="P11" s="22"/>
       <c r="S11" s="22"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="E12" s="44"/>
       <c r="H12" s="44"/>
-      <c r="O12" s="22"/>
       <c r="P12" s="22"/>
       <c r="S12" s="22"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="O13" s="22"/>
       <c r="P13" s="22"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>14</v>
@@ -5504,36 +5687,48 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C15">
-        <v>13705</v>
+        <v>11822</v>
       </c>
       <c r="D15">
-        <v>652</v>
+        <v>1603</v>
       </c>
       <c r="E15">
-        <v>6233</v>
+        <v>5168</v>
       </c>
       <c r="F15">
-        <v>82278</v>
+        <v>61264</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16">
+        <v>3777</v>
+      </c>
+      <c r="D16">
+        <v>3603</v>
+      </c>
+      <c r="E16">
+        <v>5768</v>
+      </c>
+      <c r="F16">
+        <v>7657</v>
+      </c>
+      <c r="H16" t="s">
         <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" t="s">
-        <v>52</v>
       </c>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
@@ -5541,15 +5736,15 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="O17" s="22" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="P17">
         <v>27163</v>
@@ -5557,10 +5752,8 @@
       <c r="S17" s="22"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="L18" s="51"/>
-      <c r="M18" s="63"/>
       <c r="O18" s="22" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="P18">
         <v>10865</v>
@@ -5571,7 +5764,7 @@
       <c r="L19" s="51"/>
       <c r="M19" s="51"/>
       <c r="O19" s="22" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="P19">
         <v>200</v>
@@ -5580,15 +5773,15 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>180</v>
+        <v>349</v>
       </c>
       <c r="C20" t="s">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="L20" s="51"/>
       <c r="M20" s="52"/>
       <c r="O20" s="22" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="P20">
         <v>1500</v>
@@ -5597,28 +5790,28 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="O21" s="22" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="P21">
         <v>3000</v>
@@ -5627,28 +5820,28 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="D22">
-        <v>2334</v>
+        <v>3170</v>
       </c>
       <c r="E22">
         <v>2961</v>
       </c>
       <c r="F22" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="G22" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="O22" s="22" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="P22">
         <v>21881</v>
@@ -5660,25 +5853,25 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="D23">
-        <v>282</v>
+        <v>447</v>
       </c>
       <c r="E23">
         <v>404</v>
       </c>
       <c r="F23" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="G23" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="O23" s="22" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="P23">
         <v>21635</v>
@@ -5687,28 +5880,28 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="D24">
-        <v>45705</v>
+        <v>58496</v>
       </c>
       <c r="E24">
-        <v>45998</v>
+        <v>57997</v>
       </c>
       <c r="F24" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="G24" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="P24">
         <v>1500</v>
@@ -5717,28 +5910,28 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="D25">
-        <v>27084</v>
+        <v>37127</v>
       </c>
       <c r="E25">
-        <v>27510</v>
+        <v>37513</v>
       </c>
       <c r="F25" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="G25" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="P25" s="22">
         <v>-1800</v>
@@ -5747,28 +5940,28 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="D26">
-        <v>24365</v>
+        <v>33483</v>
       </c>
       <c r="E26">
-        <v>24011</v>
+        <v>32014</v>
       </c>
       <c r="F26" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="G26" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="O26" s="22" t="s">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="P26" s="22">
         <v>-200</v>
@@ -5777,28 +5970,28 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="D27">
-        <v>5859</v>
+        <v>5758</v>
       </c>
       <c r="E27">
         <v>5000</v>
       </c>
       <c r="F27" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="G27" t="s">
-        <v>219</v>
+        <v>330</v>
       </c>
       <c r="O27" s="22" t="s">
-        <v>244</v>
+        <v>199</v>
       </c>
       <c r="P27" s="22">
         <v>-3532</v>
@@ -5807,16 +6000,16 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="D28">
-        <v>48612</v>
+        <v>54514</v>
       </c>
       <c r="E28">
         <v>50340</v>
@@ -5825,7 +6018,7 @@
         <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>220</v>
+        <v>347</v>
       </c>
       <c r="O28" s="22"/>
       <c r="P28" s="22"/>
@@ -5833,25 +6026,25 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="D29">
-        <v>3890</v>
+        <v>4377</v>
       </c>
       <c r="E29">
         <v>4557</v>
       </c>
       <c r="F29" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="G29" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
@@ -5859,25 +6052,25 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="D30">
-        <v>2545</v>
+        <v>2315</v>
       </c>
       <c r="E30">
         <v>3557</v>
       </c>
       <c r="F30" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="G30" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="O30" s="22"/>
       <c r="P30" s="22"/>
@@ -5885,25 +6078,25 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="D31">
-        <v>11845</v>
+        <v>17451.25</v>
       </c>
       <c r="E31">
         <v>14950</v>
       </c>
       <c r="F31" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="G31" t="s">
-        <v>222</v>
+        <v>347</v>
       </c>
       <c r="O31" s="22"/>
       <c r="P31" s="22"/>
@@ -5911,25 +6104,25 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="D32">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="E32">
         <v>437</v>
       </c>
       <c r="F32" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="G32" t="s">
-        <v>221</v>
+        <v>347</v>
       </c>
       <c r="O32" s="22"/>
       <c r="P32" s="22"/>
@@ -5937,606 +6130,2139 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="D33">
-        <v>3004</v>
+        <v>3939</v>
       </c>
       <c r="E33">
         <v>3266</v>
       </c>
       <c r="F33" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="G33" t="s">
-        <v>221</v>
+        <v>347</v>
       </c>
       <c r="O33" s="22"/>
       <c r="P33" s="22"/>
       <c r="S33" s="22"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>361</v>
+      </c>
       <c r="D34">
         <f>SUM(D22:D33)</f>
-        <v>175914</v>
-      </c>
-      <c r="E34">
+        <v>221447.25</v>
+      </c>
+      <c r="E34" s="85">
         <f>SUM(E22:E33)</f>
-        <v>182991</v>
+        <v>212996</v>
+      </c>
+      <c r="F34" t="s">
+        <v>359</v>
       </c>
       <c r="O34" s="22"/>
       <c r="P34" s="22"/>
       <c r="S34" s="22"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="D35" s="14">
+      <c r="C35" t="s">
+        <v>358</v>
+      </c>
+      <c r="D35" s="83">
         <f>100-(E34*100)/D34</f>
-        <v>-4.0229885057471222</v>
-      </c>
-      <c r="E35">
+        <v>3.8163716189747277</v>
+      </c>
+      <c r="E35" s="84">
         <f>E34*1.12</f>
-        <v>204949.92</v>
+        <v>238555.52000000002</v>
+      </c>
+      <c r="F35" t="s">
+        <v>360</v>
       </c>
       <c r="O35" s="22"/>
       <c r="P35" s="22"/>
       <c r="S35" s="22"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
-        <v>171</v>
-      </c>
+      <c r="D36" s="14"/>
       <c r="O36" s="22"/>
       <c r="P36" s="22"/>
       <c r="S36" s="22"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="H37" t="s">
-        <v>111</v>
-      </c>
-      <c r="J37" t="s">
-        <v>109</v>
-      </c>
-      <c r="K37" t="s">
-        <v>110</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="D37" s="14"/>
       <c r="O37" s="22"/>
       <c r="P37" s="22"/>
       <c r="S37" s="22"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
+        <v>333</v>
+      </c>
       <c r="B38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="2">
-        <v>50000</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2">
-        <f>15426.88+19500</f>
-        <v>34926.879999999997</v>
-      </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2">
-        <v>7500</v>
-      </c>
-      <c r="K38" s="2">
-        <v>7500</v>
+        <v>334</v>
+      </c>
+      <c r="C38" t="s">
+        <v>335</v>
+      </c>
+      <c r="D38" t="s">
+        <v>336</v>
+      </c>
+      <c r="E38" t="s">
+        <v>341</v>
+      </c>
+      <c r="F38" t="s">
+        <v>127</v>
       </c>
       <c r="O38" s="22"/>
       <c r="P38" s="22"/>
       <c r="S38" s="22"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>331</v>
+      </c>
       <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39">
-        <f>32000</f>
-        <v>32000</v>
-      </c>
-      <c r="D39" t="s">
-        <v>118</v>
+        <v>332</v>
+      </c>
+      <c r="C39" t="s">
+        <v>337</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>338</v>
       </c>
       <c r="E39" t="s">
-        <v>117</v>
-      </c>
-      <c r="J39">
-        <f>3305120+295000+250000</f>
-        <v>3850120</v>
-      </c>
-      <c r="K39">
-        <v>4000000</v>
+        <v>346</v>
       </c>
       <c r="O39" s="22"/>
       <c r="P39" s="22"/>
       <c r="S39" s="22"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>339</v>
+      </c>
       <c r="B40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40">
-        <f>6000+50000+61000+37500</f>
-        <v>154500</v>
-      </c>
-      <c r="D40" t="s">
-        <v>103</v>
+        <v>340</v>
+      </c>
+      <c r="D40" s="14">
+        <f>3300*12</f>
+        <v>39600</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F40" t="s">
-        <v>105</v>
-      </c>
-      <c r="G40" t="s">
-        <v>106</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="O40" s="22"/>
       <c r="P40" s="22"/>
       <c r="S40" s="22"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>343</v>
+      </c>
       <c r="B41" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41">
-        <f>3365+26804</f>
-        <v>30169</v>
+        <v>344</v>
+      </c>
+      <c r="D41" s="14"/>
+      <c r="F41" t="s">
+        <v>345</v>
       </c>
       <c r="O41" s="22"/>
       <c r="P41" s="22"/>
       <c r="S41" s="22"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="G42">
-        <f>42601-800</f>
-        <v>41801</v>
-      </c>
-      <c r="H42">
-        <v>12</v>
-      </c>
-      <c r="I42">
-        <f>H42*G42</f>
-        <v>501612</v>
-      </c>
-      <c r="J42" s="18">
-        <f>I42*1.1</f>
-        <v>551773.20000000007</v>
-      </c>
-      <c r="K42" s="18">
-        <f>J42-186500</f>
-        <v>365273.20000000007</v>
-      </c>
+      <c r="D42" s="14"/>
       <c r="O42" s="22"/>
-      <c r="P42" s="21"/>
+      <c r="P42" s="22"/>
       <c r="S42" s="22"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="G43">
-        <v>33300</v>
-      </c>
-      <c r="H43">
-        <v>12</v>
-      </c>
-      <c r="I43">
-        <f>G43*H43</f>
-        <v>399600</v>
-      </c>
-      <c r="J43" s="18">
-        <f>I43*1.1</f>
-        <v>439560.00000000006</v>
-      </c>
-      <c r="K43" s="18">
-        <f>J43-186500</f>
-        <v>253060.00000000006</v>
-      </c>
+      <c r="A43" s="5"/>
       <c r="O43" s="22"/>
       <c r="P43" s="22"/>
       <c r="S43" s="22"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="G44" s="1">
-        <v>14500</v>
-      </c>
-      <c r="H44" s="1">
-        <v>12</v>
-      </c>
-      <c r="I44" s="1">
-        <f>G44*H44</f>
-        <v>174000</v>
-      </c>
-      <c r="J44" s="1">
-        <f>I44*1.1</f>
-        <v>191400.00000000003</v>
-      </c>
-      <c r="K44" s="1">
-        <f>J44-118000</f>
-        <v>73400.000000000029</v>
+      <c r="A44" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H44" t="s">
+        <v>103</v>
+      </c>
+      <c r="J44" t="s">
+        <v>101</v>
+      </c>
+      <c r="K44" t="s">
+        <v>102</v>
       </c>
       <c r="O44" s="22"/>
       <c r="P44" s="22"/>
       <c r="S44" s="22"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="F45" t="s">
-        <v>112</v>
-      </c>
-      <c r="G45">
-        <v>39501</v>
-      </c>
-      <c r="H45">
-        <f>12*G45</f>
-        <v>474012</v>
-      </c>
-      <c r="I45">
-        <f>G45*100/56301</f>
-        <v>70.160387914957099</v>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="2">
+        <v>50000</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2">
+        <f>15426.88+19500</f>
+        <v>34926.879999999997</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2">
+        <v>7500</v>
+      </c>
+      <c r="K45" s="2">
+        <v>7500</v>
       </c>
       <c r="O45" s="22"/>
       <c r="P45" s="22"/>
       <c r="S45" s="22"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="F46" t="s">
-        <v>113</v>
-      </c>
-      <c r="G46">
-        <v>16602</v>
-      </c>
-      <c r="H46">
-        <f>12*G46</f>
-        <v>199224</v>
-      </c>
-      <c r="I46">
-        <f>G46*100/56301</f>
-        <v>29.487930942612032</v>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46">
+        <f>32000</f>
+        <v>32000</v>
+      </c>
+      <c r="D46" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" t="s">
+        <v>108</v>
+      </c>
+      <c r="J46">
+        <f>3305120+295000+250000</f>
+        <v>3850120</v>
+      </c>
+      <c r="K46">
+        <v>4000000</v>
       </c>
       <c r="O46" s="22"/>
       <c r="P46" s="22"/>
       <c r="S46" s="22"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A47" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="K47" s="14"/>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <f>6000+50000+61000+37500</f>
+        <v>154500</v>
+      </c>
+      <c r="D47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" t="s">
+        <v>97</v>
+      </c>
+      <c r="G47" t="s">
+        <v>98</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="O47" s="22"/>
       <c r="P47" s="22"/>
       <c r="S47" s="22"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A48" s="5"/>
       <c r="B48" t="s">
-        <v>215</v>
-      </c>
-      <c r="K48" s="14"/>
+        <v>100</v>
+      </c>
+      <c r="C48">
+        <f>3365+26804</f>
+        <v>30169</v>
+      </c>
       <c r="O48" s="22"/>
       <c r="P48" s="22"/>
       <c r="S48" s="22"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A49" s="5"/>
-      <c r="B49" t="s">
-        <v>216</v>
-      </c>
-      <c r="K49" s="14"/>
+      <c r="G49">
+        <f>42601-800</f>
+        <v>41801</v>
+      </c>
+      <c r="H49">
+        <v>12</v>
+      </c>
+      <c r="I49">
+        <f>H49*G49</f>
+        <v>501612</v>
+      </c>
+      <c r="J49" s="18">
+        <f>I49*1.1</f>
+        <v>551773.20000000007</v>
+      </c>
+      <c r="K49" s="18">
+        <f>J49-186500</f>
+        <v>365273.20000000007</v>
+      </c>
       <c r="O49" s="22"/>
-      <c r="P49" s="22"/>
+      <c r="P49" s="21"/>
       <c r="S49" s="22"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A50" s="5"/>
-      <c r="B50" t="s">
-        <v>285</v>
-      </c>
-      <c r="C50" t="s">
-        <v>286</v>
-      </c>
-      <c r="D50" t="s">
-        <v>287</v>
-      </c>
-      <c r="K50" s="14"/>
+      <c r="G50">
+        <v>33300</v>
+      </c>
+      <c r="H50">
+        <v>12</v>
+      </c>
+      <c r="I50">
+        <f>G50*H50</f>
+        <v>399600</v>
+      </c>
+      <c r="J50" s="18">
+        <f>I50*1.1</f>
+        <v>439560.00000000006</v>
+      </c>
+      <c r="K50" s="18">
+        <f>J50-186500</f>
+        <v>253060.00000000006</v>
+      </c>
       <c r="O50" s="22"/>
       <c r="P50" s="22"/>
       <c r="S50" s="22"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A51" s="5"/>
-      <c r="K51" s="14"/>
+      <c r="G51" s="1">
+        <v>14500</v>
+      </c>
+      <c r="H51" s="1">
+        <v>12</v>
+      </c>
+      <c r="I51" s="1">
+        <f>G51*H51</f>
+        <v>174000</v>
+      </c>
+      <c r="J51" s="1">
+        <f>I51*1.1</f>
+        <v>191400.00000000003</v>
+      </c>
+      <c r="K51" s="1">
+        <f>J51-118000</f>
+        <v>73400.000000000029</v>
+      </c>
       <c r="O51" s="22"/>
       <c r="P51" s="22"/>
       <c r="S51" s="22"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A52" s="5"/>
-      <c r="K52" s="14"/>
+      <c r="F52" t="s">
+        <v>104</v>
+      </c>
+      <c r="G52">
+        <v>39501</v>
+      </c>
+      <c r="H52">
+        <f>12*G52</f>
+        <v>474012</v>
+      </c>
+      <c r="I52">
+        <f>G52*100/56301</f>
+        <v>70.160387914957099</v>
+      </c>
       <c r="O52" s="22"/>
       <c r="P52" s="22"/>
       <c r="S52" s="22"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A53" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K53" s="14"/>
+      <c r="F53" t="s">
+        <v>105</v>
+      </c>
+      <c r="G53">
+        <v>16602</v>
+      </c>
+      <c r="H53">
+        <f>12*G53</f>
+        <v>199224</v>
+      </c>
+      <c r="I53">
+        <f>G53*100/56301</f>
+        <v>29.487930942612032</v>
+      </c>
       <c r="O53" s="22"/>
       <c r="P53" s="22"/>
       <c r="S53" s="22"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A54" s="32">
-        <v>10850</v>
-      </c>
-      <c r="B54" t="s">
-        <v>151</v>
-      </c>
-      <c r="C54" t="s">
-        <v>158</v>
-      </c>
-      <c r="D54" t="s">
-        <v>152</v>
-      </c>
-      <c r="E54" t="s">
-        <v>153</v>
-      </c>
-      <c r="F54" t="s">
-        <v>156</v>
-      </c>
-      <c r="G54" t="s">
-        <v>154</v>
-      </c>
-      <c r="H54" t="s">
-        <v>157</v>
-      </c>
-      <c r="I54" t="s">
-        <v>159</v>
-      </c>
       <c r="O54" s="22"/>
       <c r="P54" s="22"/>
       <c r="S54" s="22"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A55" s="32">
-        <f>SUM(C61:H61)</f>
-        <v>11712.42</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" s="22">
-        <v>1894</v>
-      </c>
-      <c r="D55" s="22">
-        <v>1749</v>
-      </c>
-      <c r="E55">
-        <v>145</v>
-      </c>
-      <c r="F55">
-        <f t="shared" ref="F55:F60" si="0">E55*18%</f>
-        <v>26.099999999999998</v>
-      </c>
-      <c r="G55" s="22">
-        <v>9101</v>
-      </c>
-      <c r="H55" s="22">
-        <f t="shared" ref="H55:H60" si="1">SUM(D55:F55)</f>
-        <v>1920.1</v>
-      </c>
-      <c r="I55" s="22">
-        <f t="shared" ref="I55:I60" si="2">2000-H55</f>
-        <v>79.900000000000091</v>
-      </c>
+      <c r="A55" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="K55" s="14"/>
       <c r="O55" s="22"/>
       <c r="P55" s="22"/>
       <c r="S55" s="22"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56" s="22">
-        <v>1894</v>
-      </c>
-      <c r="D56" s="22">
-        <v>1773</v>
-      </c>
-      <c r="E56">
-        <v>121</v>
-      </c>
-      <c r="F56">
-        <f t="shared" si="0"/>
-        <v>21.779999999999998</v>
-      </c>
-      <c r="G56" s="22">
-        <v>7329</v>
-      </c>
-      <c r="H56" s="22">
-        <f t="shared" si="1"/>
-        <v>1915.78</v>
-      </c>
-      <c r="I56" s="22">
-        <f t="shared" si="2"/>
-        <v>84.220000000000027</v>
-      </c>
+      <c r="A56" s="5"/>
+      <c r="B56" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" t="s">
+        <v>352</v>
+      </c>
+      <c r="D56" t="s">
+        <v>353</v>
+      </c>
+      <c r="E56" t="s">
+        <v>354</v>
+      </c>
+      <c r="K56" s="14"/>
       <c r="O56" s="22"/>
       <c r="P56" s="22"/>
+      <c r="S56" s="22"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B57">
-        <v>3</v>
-      </c>
-      <c r="C57" s="22">
-        <v>1894</v>
-      </c>
-      <c r="D57" s="22">
-        <v>1796</v>
-      </c>
-      <c r="E57">
-        <v>98</v>
-      </c>
-      <c r="F57">
-        <f t="shared" si="0"/>
-        <v>17.64</v>
-      </c>
-      <c r="G57" s="22">
-        <v>5533</v>
-      </c>
-      <c r="H57" s="22">
-        <f t="shared" si="1"/>
-        <v>1911.64</v>
-      </c>
-      <c r="I57" s="22">
-        <f t="shared" si="2"/>
-        <v>88.3599999999999</v>
-      </c>
+      <c r="A57" s="5"/>
+      <c r="B57" t="s">
+        <v>177</v>
+      </c>
+      <c r="K57" s="14"/>
+      <c r="O57" s="22"/>
+      <c r="P57" s="22"/>
+      <c r="S57" s="22"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B58">
-        <v>4</v>
-      </c>
-      <c r="C58" s="22">
-        <v>1894</v>
-      </c>
-      <c r="D58" s="22">
-        <v>1820</v>
-      </c>
-      <c r="E58">
-        <v>74</v>
-      </c>
-      <c r="F58">
-        <f t="shared" si="0"/>
-        <v>13.32</v>
-      </c>
-      <c r="G58" s="22">
-        <v>3713</v>
-      </c>
-      <c r="H58" s="22">
-        <f t="shared" si="1"/>
-        <v>1907.32</v>
-      </c>
-      <c r="I58" s="22">
-        <f t="shared" si="2"/>
-        <v>92.680000000000064</v>
-      </c>
+      <c r="A58" s="5"/>
+      <c r="B58" t="s">
+        <v>239</v>
+      </c>
+      <c r="C58" t="s">
+        <v>240</v>
+      </c>
+      <c r="D58" t="s">
+        <v>241</v>
+      </c>
+      <c r="K58" s="14"/>
+      <c r="O58" s="22"/>
+      <c r="P58" s="22"/>
+      <c r="S58" s="22"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B59">
-        <v>5</v>
-      </c>
-      <c r="C59" s="22">
-        <v>1894</v>
-      </c>
-      <c r="D59" s="22">
-        <v>1844</v>
-      </c>
-      <c r="E59">
-        <v>50</v>
-      </c>
-      <c r="F59">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G59" s="22">
-        <v>1869</v>
-      </c>
-      <c r="H59" s="22">
-        <f t="shared" si="1"/>
-        <v>1903</v>
-      </c>
-      <c r="I59" s="22">
-        <f t="shared" si="2"/>
-        <v>97</v>
-      </c>
+      <c r="A59" s="5"/>
+      <c r="K59" s="14"/>
+      <c r="O59" s="22"/>
+      <c r="P59" s="22"/>
+      <c r="S59" s="22"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B60">
-        <v>6</v>
-      </c>
-      <c r="C60" s="22">
-        <v>1894</v>
-      </c>
-      <c r="D60" s="22">
-        <v>1869</v>
-      </c>
-      <c r="E60">
-        <v>25</v>
-      </c>
-      <c r="F60">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60" s="22">
-        <f t="shared" si="1"/>
-        <v>1898.5</v>
-      </c>
-      <c r="I60" s="22">
-        <f t="shared" si="2"/>
-        <v>101.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B61" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C61">
-        <v>256.08000000000004</v>
-      </c>
-      <c r="H61" s="22">
-        <f>SUM(H55:H60)</f>
-        <v>11456.34</v>
-      </c>
-      <c r="I61" s="22" cm="1">
-        <f t="array" ref="I61">SUM(VALUE(I55:I60))</f>
-        <v>543.66000000000008</v>
-      </c>
+      <c r="A60" s="5"/>
+      <c r="K60" s="14"/>
+      <c r="O60" s="22"/>
+      <c r="P60" s="22"/>
+      <c r="S60" s="22"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="K61" s="14"/>
+      <c r="O61" s="22"/>
+      <c r="P61" s="22"/>
+      <c r="S61" s="22"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>362</v>
+      </c>
+      <c r="B62" t="s">
+        <v>363</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>365</v>
+      </c>
+      <c r="E62" t="s">
+        <v>366</v>
+      </c>
+      <c r="F62" t="s">
+        <v>367</v>
+      </c>
+      <c r="G62" t="s">
+        <v>368</v>
+      </c>
+      <c r="O62" s="22"/>
+      <c r="P62" s="22"/>
+      <c r="S62" s="22"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>715000</v>
+      </c>
+      <c r="B63" t="s">
+        <v>364</v>
+      </c>
+      <c r="C63">
+        <v>10987</v>
+      </c>
+      <c r="D63">
+        <v>591093</v>
+      </c>
+      <c r="E63" s="21">
+        <v>207800</v>
+      </c>
+      <c r="F63" s="21">
+        <v>73859</v>
+      </c>
+      <c r="G63">
+        <v>50762</v>
+      </c>
+      <c r="O63" s="22"/>
+      <c r="P63" s="22"/>
+      <c r="S63" s="22"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="O64" s="22"/>
+      <c r="P64" s="22"/>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C65" s="54"/>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C66" s="54"/>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C67" s="54"/>
+      <c r="D67" s="54"/>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C68" s="54"/>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C69" s="54"/>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C70" s="54"/>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C71" s="54"/>
+      <c r="D71" s="54"/>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C77" s="54"/>
+      <c r="D77" s="54"/>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C81" s="54"/>
+      <c r="D81" s="54"/>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C83" s="54"/>
+      <c r="D83" s="54"/>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C84" s="54"/>
+      <c r="D84" s="54"/>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C85" s="54"/>
+      <c r="D85" s="54"/>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C86" s="54"/>
+      <c r="D86" s="54"/>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C87" s="54"/>
+      <c r="D87" s="54"/>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C88" s="54"/>
+      <c r="D88" s="54"/>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C89" s="54"/>
+      <c r="D89" s="54"/>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C91" s="54"/>
+      <c r="D91" s="54"/>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C92" s="54"/>
+      <c r="D92" s="54"/>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
+    </row>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C94" s="54"/>
+      <c r="D94" s="54"/>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C95" s="54"/>
+      <c r="D95" s="54"/>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C96" s="54"/>
+      <c r="D96" s="54"/>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C97" s="54"/>
+      <c r="D97" s="54"/>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C99" s="54"/>
+      <c r="D99" s="54"/>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C101" s="54"/>
+      <c r="D101" s="54"/>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C102" s="54"/>
+      <c r="D102" s="54"/>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C103" s="54"/>
+      <c r="D103" s="54"/>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C104" s="54"/>
+      <c r="D104" s="54"/>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C105" s="54"/>
+      <c r="D105" s="54"/>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C106" s="54"/>
+      <c r="D106" s="54"/>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C107" s="54"/>
+      <c r="D107" s="54"/>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C108" s="54"/>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C109" s="54"/>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C110" s="54"/>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C111" s="54"/>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C112" s="54"/>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C113" s="54"/>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C114" s="54"/>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C115" s="54"/>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C116" s="54"/>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C117" s="54"/>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C118" s="54"/>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C119" s="54"/>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C120" s="54"/>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C121" s="54"/>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C122" s="54"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D35">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="D35:D37 D39:D42">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThan">
       <formula>$E$35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D34:E34">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
+  <conditionalFormatting sqref="D34">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="greaterThan">
+      <formula>$E$34</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="lessThan">
+      <formula>$E$34</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D34:E34 E35">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7DD2E2-FF1A-4BB9-A01E-B2195D3FEF92}">
+  <dimension ref="A1:L75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="67.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="32">
+        <v>504209</v>
+      </c>
+      <c r="D3" s="32">
+        <v>657620</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="32">
+        <v>13876</v>
+      </c>
+      <c r="D4" s="32">
+        <v>29392</v>
+      </c>
+      <c r="I4" t="s">
+        <v>203</v>
+      </c>
+      <c r="J4" s="32">
+        <v>504209</v>
+      </c>
+      <c r="K4" s="32">
+        <v>657620</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="32">
+        <v>9252</v>
+      </c>
+      <c r="D5" s="32">
+        <v>24768</v>
+      </c>
+      <c r="I5" t="s">
+        <v>204</v>
+      </c>
+      <c r="J5" s="32">
+        <v>13876</v>
+      </c>
+      <c r="K5" s="32">
+        <v>29392</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>205</v>
+      </c>
+      <c r="J6" s="32">
+        <v>9252</v>
+      </c>
+      <c r="K6" s="32">
+        <v>24768</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8">
+        <v>605221</v>
+      </c>
+      <c r="I8" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" t="s">
+        <v>207</v>
+      </c>
+      <c r="J9">
+        <v>605221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10">
+        <v>21600</v>
+      </c>
+      <c r="H10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I10" t="s">
+        <v>221</v>
+      </c>
+      <c r="J10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11">
+        <v>48414</v>
+      </c>
+      <c r="H11" t="s">
+        <v>226</v>
+      </c>
+      <c r="I11" t="s">
+        <v>208</v>
+      </c>
+      <c r="J11">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12">
+        <v>30998</v>
+      </c>
+      <c r="D12" s="44">
+        <f>2999.85*12</f>
+        <v>35998.199999999997</v>
+      </c>
+      <c r="H12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I12" t="s">
+        <v>209</v>
+      </c>
+      <c r="J12">
+        <v>48414</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="44"/>
+      <c r="H13" t="s">
+        <v>226</v>
+      </c>
+      <c r="I13" t="s">
+        <v>210</v>
+      </c>
+      <c r="J13">
+        <v>30998</v>
+      </c>
+      <c r="K13" s="44">
+        <f>2999.85*12</f>
+        <v>35998.199999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="44">
+        <f>8*3000</f>
+        <v>24000</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="44">
+        <v>8000</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="J15" s="44">
+        <f>8*3000</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16">
+        <v>504210</v>
+      </c>
+      <c r="D16">
+        <f>C17-12500</f>
+        <v>842</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="J16" s="44">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17">
+        <v>13342</v>
+      </c>
+      <c r="H17" t="s">
+        <v>226</v>
+      </c>
+      <c r="I17" t="s">
+        <v>211</v>
+      </c>
+      <c r="J17">
+        <v>504210</v>
+      </c>
+      <c r="K17">
+        <f>J18-12500</f>
+        <v>842</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>226</v>
+      </c>
+      <c r="I18" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18">
+        <v>13342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>226</v>
+      </c>
+      <c r="I19" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20">
+        <v>534</v>
+      </c>
+      <c r="H20" t="s">
+        <v>226</v>
+      </c>
+      <c r="I20" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>226</v>
+      </c>
+      <c r="I21" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22">
+        <v>13876</v>
+      </c>
+      <c r="H22" t="s">
+        <v>226</v>
+      </c>
+      <c r="I22" t="s">
+        <v>216</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23">
+        <v>4624</v>
+      </c>
+      <c r="H23" t="s">
+        <v>226</v>
+      </c>
+      <c r="I23" t="s">
+        <v>217</v>
+      </c>
+      <c r="J23">
+        <v>13876</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24">
+        <v>9252</v>
+      </c>
+      <c r="I24" t="s">
+        <v>218</v>
+      </c>
+      <c r="J24">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25">
+        <v>1156</v>
+      </c>
+      <c r="I25" t="s">
+        <v>219</v>
+      </c>
+      <c r="J25">
+        <v>9252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I26" t="s">
+        <v>220</v>
+      </c>
+      <c r="J26">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>251</v>
+      </c>
+      <c r="B29" s="54">
+        <v>24038</v>
+      </c>
+      <c r="C29" s="54">
+        <v>288456</v>
+      </c>
+      <c r="I29" s="21"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="54">
+        <v>9615</v>
+      </c>
+      <c r="C30" s="54">
+        <v>115380</v>
+      </c>
+      <c r="D30" s="14">
+        <f>C30*100/C29</f>
+        <v>39.999167984025291</v>
+      </c>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B31">
+        <v>200</v>
+      </c>
+      <c r="C31" s="54">
+        <v>2400</v>
+      </c>
+      <c r="D31" s="14">
+        <f>C31*100/C29</f>
+        <v>0.8320159747067144</v>
+      </c>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>248</v>
+      </c>
+      <c r="B32" s="54">
+        <v>1500</v>
+      </c>
+      <c r="C32" s="54">
+        <v>18000</v>
+      </c>
+      <c r="D32" s="14">
+        <f>C32*100/C29</f>
+        <v>6.2401198103003575</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" s="54">
+        <v>3000</v>
+      </c>
+      <c r="C33" s="54">
+        <v>36000</v>
+      </c>
+      <c r="D33" s="14">
+        <f>C33*100/C29</f>
+        <v>12.480239620600715</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="54">
+        <v>1500</v>
+      </c>
+      <c r="C34" s="54">
+        <v>18000</v>
+      </c>
+      <c r="D34" s="14">
+        <f>C34*100/C29</f>
+        <v>6.2401198103003575</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>250</v>
+      </c>
+      <c r="B35" s="54">
+        <v>18444</v>
+      </c>
+      <c r="C35" s="54">
+        <v>221328</v>
+      </c>
+      <c r="D35" s="14">
+        <f>C35*100/C29</f>
+        <v>76.728513187453203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>254</v>
+      </c>
+      <c r="B36" s="54">
+        <f>SUM(B30:B35)</f>
+        <v>34259</v>
+      </c>
+      <c r="C36" s="54">
+        <f>SUM(C30:C35)</f>
+        <v>411108</v>
+      </c>
+      <c r="D36" s="14">
+        <f>C36*100/C29</f>
+        <v>142.52017638738664</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I39" s="14"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A41" s="70" t="s">
+        <v>323</v>
+      </c>
+      <c r="B41" s="70" t="s">
+        <v>322</v>
+      </c>
+      <c r="C41" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="D41" s="72" t="s">
+        <v>321</v>
+      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42" s="73"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="82">
+        <v>97000</v>
+      </c>
+      <c r="D42" s="81">
+        <v>56200</v>
+      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43" s="73" t="s">
+        <v>299</v>
+      </c>
+      <c r="B43" s="73">
+        <v>30</v>
+      </c>
+      <c r="C43" s="74">
+        <f>+C42*B43%</f>
+        <v>29100</v>
+      </c>
+      <c r="D43" s="75">
+        <v>19500</v>
+      </c>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A44" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="B44" s="73">
+        <v>30</v>
+      </c>
+      <c r="C44" s="74">
+        <f>+C42*B44%</f>
+        <v>29100</v>
+      </c>
+      <c r="D44" s="75">
+        <v>15000</v>
+      </c>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A45" s="73" t="s">
+        <v>298</v>
+      </c>
+      <c r="B45" s="73">
+        <v>30</v>
+      </c>
+      <c r="C45" s="74">
+        <f>+C42*B45%</f>
+        <v>29100</v>
+      </c>
+      <c r="D45" s="76">
+        <v>21700</v>
+      </c>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="I45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A46" s="73" t="s">
+        <v>297</v>
+      </c>
+      <c r="B46" s="73">
+        <v>10</v>
+      </c>
+      <c r="C46" s="74">
+        <f>+C42*B46%</f>
+        <v>9700</v>
+      </c>
+      <c r="D46" s="76"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="I46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="I47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A49" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A50" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="H50" s="69" t="s">
+        <v>315</v>
+      </c>
+      <c r="K50" s="22"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A51" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="C51" s="12">
+        <v>6000</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A52" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="C52" s="12">
+        <v>3000</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A53" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="C53">
+        <v>3000</v>
+      </c>
+      <c r="D53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>53</v>
+      </c>
+      <c r="F53" t="s">
+        <v>137</v>
+      </c>
+      <c r="G53" t="s">
+        <v>302</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A54" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>1000</v>
+      </c>
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54" t="s">
+        <v>137</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="J54" s="22"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A55" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55">
+        <v>2500</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+      <c r="E55" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55" t="s">
+        <v>137</v>
+      </c>
+      <c r="G55" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A56" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56">
+        <v>1500</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" t="s">
+        <v>137</v>
+      </c>
+      <c r="G56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A57" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="C57">
+        <v>500</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" t="s">
+        <v>54</v>
+      </c>
+      <c r="F57" t="s">
+        <v>137</v>
+      </c>
+      <c r="G57" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A58" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="C58">
+        <v>1000</v>
+      </c>
+      <c r="D58" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" t="s">
+        <v>54</v>
+      </c>
+      <c r="F58" t="s">
+        <v>137</v>
+      </c>
+      <c r="G58" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A59" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="41" t="s">
+        <v>305</v>
+      </c>
+      <c r="C59" s="11">
+        <v>4500</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A60" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="41" t="s">
+        <v>305</v>
+      </c>
+      <c r="C60" s="11">
+        <v>4500</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F60" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>1200</v>
+      </c>
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" t="s">
+        <v>53</v>
+      </c>
+      <c r="F61" t="s">
+        <v>137</v>
+      </c>
+      <c r="G61" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A62" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="C62">
+        <v>2001</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s">
+        <v>53</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A63" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>2500</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F63" t="s">
+        <v>137</v>
+      </c>
+      <c r="G63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A64" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64">
+        <v>11000</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64" t="s">
+        <v>53</v>
+      </c>
+      <c r="F64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C65">
+        <v>3300</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>53</v>
+      </c>
+      <c r="F65" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66">
+        <v>2000</v>
+      </c>
+      <c r="D66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" t="s">
+        <v>53</v>
+      </c>
+      <c r="F66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67">
+        <v>3500</v>
+      </c>
+      <c r="D67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" t="s">
+        <v>53</v>
+      </c>
+      <c r="F67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="79" t="s">
+        <v>51</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C68">
+        <v>3000</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" t="s">
+        <v>53</v>
+      </c>
+      <c r="F68" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="63" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="12">
+        <v>500</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" s="79" t="s">
+        <v>49</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70">
+        <v>3001</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s">
+        <v>53</v>
+      </c>
+      <c r="F70" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="C71" s="12">
+        <v>2501</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="C72" s="12">
+        <v>2501</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C73">
+        <v>800</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>53</v>
+      </c>
+      <c r="F73" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" s="80" t="s">
+        <v>329</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C74" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E74" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" s="79" t="s">
+        <v>316</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C75">
+        <v>30000</v>
+      </c>
+      <c r="F75" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="63" t="s">
+        <v>318</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D45:D46"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F50:F58 H54 G68 G50:H50 F60:F70 F72:F75">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="INVEST">
+      <formula>NOT(ISERROR(SEARCH("INVEST",F50)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50:F58 H54 G68 F60:F70 F72:F75">
+    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="Debt">
+      <formula>NOT(ISERROR(SEARCH("Debt",F50)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F51:F58 H54 G68 F60:F70 F72:F75">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+      <formula>"W/N"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="INVEST">
+      <formula>NOT(ISERROR(SEARCH("INVEST",F59)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="Debt">
+      <formula>NOT(ISERROR(SEARCH("Debt",F59)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+      <formula>"W/N"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F71">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="INVEST">
+      <formula>NOT(ISERROR(SEARCH("INVEST",F71)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F71">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Debt">
+      <formula>NOT(ISERROR(SEARCH("Debt",F71)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F71">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"W/N"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
